--- a/التقييم المالي وتكلفة الإنجاز خطوة بخطوة.xlsx
+++ b/التقييم المالي وتكلفة الإنجاز خطوة بخطوة.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Android\ADNM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B037235-24FA-4A56-91CA-24DFCA24AB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F85BDA-F9F0-4C7A-8C3C-B1FB8189ECBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A282CC02-F87B-49DB-BD0E-E61D22D90EBD}"/>
+    <workbookView xWindow="3624" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{A282CC02-F87B-49DB-BD0E-E61D22D90EBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>الوضيفة</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>اختبارات الأمان وضمان الجودة</t>
-  </si>
-  <si>
-    <t>Free</t>
   </si>
   <si>
     <t>المجموع</t>
@@ -169,12 +166,6 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -195,6 +186,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,89 +516,89 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="A2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
     </row>
     <row r="4" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4">
+        <v>11657</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5">
-        <v>14</v>
-      </c>
-      <c r="C6" s="6">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="C8" s="4">
+        <v>5828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>16</v>
-      </c>
-      <c r="C7" s="6">
-        <v>11657</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="C9" s="7">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21.6" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="6">
-        <v>5828</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8">
-        <v>5</v>
-      </c>
-      <c r="C9" s="9">
-        <v>3642</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21.6" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <f>SUM(B5:B9)</f>
         <v>49</v>
       </c>
-      <c r="C10" s="11">
-        <f>SUM(C6:C9)</f>
-        <v>31327</v>
+      <c r="C10" s="9">
+        <f>SUM(C5:C9)</f>
+        <v>35695</v>
       </c>
     </row>
   </sheetData>
